--- a/data/trans_dic/IP1014-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1014-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen defectos del habla</t>
+          <t>Menores que padecen defectos del habla (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,42 +788,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,63</t>
+          <t>0,27; 2,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,41</t>
+          <t>0,16; 1,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -897,32 +898,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 2,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -932,12 +933,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,32 +1008,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,75</t>
+          <t>0,3; 3,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1042,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,38</t>
+          <t>0,15; 1,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,53</t>
+          <t>0,0; 0,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,04</t>
+          <t>0,18; 0,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,28</t>
+          <t>0,27; 1,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,77</t>
+          <t>0,08; 0,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,59</t>
+          <t>0,1; 0,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,72</t>
+          <t>0,19; 0,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,42</t>
+          <t>0,04; 0,37</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen defectos del habla (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1583</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4818</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3219</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3452</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3150</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6329</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1384</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3218</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4823</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4328</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>614; 5878</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>642; 5453</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4746</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>617; 5393</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1097</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2256</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3219</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3298</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3221</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3645</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2106</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2106</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3524</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>622; 6362</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3516</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>621; 5574</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4691</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4041</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>6030</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2942</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4927</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1321; 6920</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2009; 9086</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>617; 5357</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1383; 8699</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2762; 11357</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>615; 5343</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1014-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1014-Habitat-trans_dic.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -803,32 +803,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,62</t>
+          <t>0,27; 2,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,34</t>
+          <t>0,16; 1,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,25</t>
+          <t>0,14; 1,18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,07</t>
+          <t>0,3; 3,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,34</t>
+          <t>0,15; 1,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1133,32 +1133,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,96</t>
+          <t>0,19; 1,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,21</t>
+          <t>0,26; 1,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,72</t>
+          <t>0,08; 0,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,62</t>
+          <t>0,1; 0,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,78</t>
+          <t>0,22; 0,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,37</t>
+          <t>0,04; 0,41</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4818</t>
+          <t>0; 5183</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3219</t>
+          <t>0; 3400</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3452</t>
+          <t>0; 4101</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3150</t>
+          <t>0; 3205</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6329</t>
+          <t>0; 5162</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3218</t>
+          <t>0; 3697</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1595,32 +1595,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4823</t>
+          <t>0; 4777</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4328</t>
+          <t>0; 3852</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>614; 5878</t>
+          <t>616; 5346</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>642; 5453</t>
+          <t>641; 5963</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4746</t>
+          <t>0; 3870</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>617; 5393</t>
+          <t>616; 5095</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2256</t>
+          <t>0; 2037</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3219</t>
+          <t>0; 3249</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3298</t>
+          <t>0; 3314</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3221</t>
+          <t>0; 3212</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3645</t>
+          <t>0; 3870</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3524</t>
+          <t>0; 3499</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>622; 6362</t>
+          <t>623; 6342</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3516</t>
+          <t>0; 3936</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>621; 5574</t>
+          <t>640; 6134</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2942</t>
+          <t>0; 3026</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4927</t>
+          <t>0; 6325</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2084,32 +2084,32 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1321; 6920</t>
+          <t>1351; 8159</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2009; 9086</t>
+          <t>1957; 9254</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>617; 5357</t>
+          <t>619; 5246</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1383; 8699</t>
+          <t>1351; 8156</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2762; 11357</t>
+          <t>3190; 11708</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>615; 5343</t>
+          <t>617; 5873</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1014-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1014-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,27 +625,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,66%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 2,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,28; 2,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,46</t>
+          <t>0,16; 1,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,18</t>
+          <t>0,14; 1,25</t>
         </is>
       </c>
     </row>
@@ -845,27 +845,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,27 +955,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,3; 2,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,47</t>
+          <t>0,15; 1,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,44</t>
+          <t>0,19; 1,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,27; 1,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,08; 0,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,13</t>
+          <t>0,0; 0,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,24</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,58</t>
+          <t>0,14; 0,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,8</t>
+          <t>0,18; 0,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,41</t>
+          <t>0,04; 0,42</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1364,27 +1364,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>896</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4269</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5183</t>
+          <t>0; 3509</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3400</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4101</t>
+          <t>0; 5342</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3205</t>
+          <t>0; 3705</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5162</t>
+          <t>0; 5159</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1384</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1384</t>
-        </is>
-      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3697</t>
+          <t>0; 4845</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3865</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>619; 5899</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4777</t>
+          <t>0; 3499</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3852</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>616; 5346</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>641; 5963</t>
+          <t>642; 5729</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3870</t>
+          <t>0; 4633</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>616; 5095</t>
+          <t>619; 5389</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1690,27 +1690,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>642</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>443</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3204</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2037</t>
+          <t>0; 3117</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3249</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3314</t>
+          <t>0; 2181</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3212</t>
+          <t>0; 3213</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3870</t>
+          <t>0; 3757</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3506</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>623; 5685</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3499</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>623; 6342</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3936</t>
+          <t>0; 3508</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>640; 6134</t>
+          <t>624; 5752</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4691</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3399</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4691</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3026</t>
+          <t>1347; 7549</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 6325</t>
+          <t>2035; 9563</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>594; 5701</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1351; 8159</t>
+          <t>0; 3590</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1957; 9254</t>
+          <t>0; 5560</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>619; 5246</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1351; 8156</t>
+          <t>1919; 8259</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3190; 11708</t>
+          <t>2671; 10538</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>617; 5873</t>
+          <t>617; 6052</t>
         </is>
       </c>
     </row>
